--- a/docs/downloads/05/tbl_agri_equip_alaotra_avaradrano.xlsx
+++ b/docs/downloads/05/tbl_agri_equip_alaotra_avaradrano.xlsx
@@ -436,12 +436,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -454,12 +448,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -472,12 +460,6 @@
           <t>Bidon (genre bidon à pétr</t>
         </is>
       </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -490,12 +472,6 @@
           <t>Buf (ex : piétinage)</t>
         </is>
       </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -508,12 +484,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -526,12 +496,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -616,12 +580,6 @@
           <t>Hafa</t>
         </is>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>0.3</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -652,12 +610,6 @@
           <t>Motoculteur, type Kubota</t>
         </is>
       </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -670,12 +622,6 @@
           <t>Nasse</t>
         </is>
       </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-      <c r="D18">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -742,12 +688,6 @@
           <t>Sarcleuse</t>
         </is>
       </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -760,12 +700,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -778,12 +712,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -796,12 +724,6 @@
           <t>Soubique, produits de tis</t>
         </is>
       </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -814,12 +736,6 @@
           <t>Tracteur</t>
         </is>
       </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -881,12 +797,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C30">
-        <v>3</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -899,12 +809,6 @@
           <t>Barre à mine</t>
         </is>
       </c>
-      <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -917,12 +821,6 @@
           <t>Bicyclette</t>
         </is>
       </c>
-      <c r="C32">
-        <v>4</v>
-      </c>
-      <c r="D32">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -953,12 +851,6 @@
           <t>Brouette</t>
         </is>
       </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -989,12 +881,6 @@
           <t>Camion</t>
         </is>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1007,12 +893,6 @@
           <t>Charrette attelée (à trac</t>
         </is>
       </c>
-      <c r="C37">
-        <v>3</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1025,12 +905,6 @@
           <t>Charrette non attelée (à</t>
         </is>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1079,12 +953,6 @@
           <t>Egreneuse</t>
         </is>
       </c>
-      <c r="C41">
-        <v>3</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1277,12 +1145,6 @@
           <t>Rouleau</t>
         </is>
       </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1331,12 +1193,6 @@
           <t>Scie</t>
         </is>
       </c>
-      <c r="C55">
-        <v>4</v>
-      </c>
-      <c r="D55">
-        <v>0.1</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1349,12 +1205,6 @@
           <t>Semoir attelé</t>
         </is>
       </c>
-      <c r="C56">
-        <v>3</v>
-      </c>
-      <c r="D56">
-        <v>0</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1366,12 +1216,6 @@
         <is>
           <t>Soubique, produits de tis</t>
         </is>
-      </c>
-      <c r="C57">
-        <v>2</v>
-      </c>
-      <c r="D57">
-        <v>0</v>
       </c>
     </row>
     <row r="58">
